--- a/data.xlsx
+++ b/data.xlsx
@@ -2388,7 +2388,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-06T10:57:44</t>
+          <t>2026-09-07T12:33:50</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2388,7 +2388,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-07T12:33:50</t>
+          <t>2026-09-08T11:20:00</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2388,7 +2388,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-08T11:20:00</t>
+          <t>2026-09-09T11:24:19</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2388,7 +2388,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-09T11:24:19</t>
+          <t>2026-09-10T11:20:47</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2707,6 +2707,377 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>2026-09-10T11:20:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>&lt; 40 HP</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8829</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9568</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>76969</v>
+      </c>
+      <c r="H44" t="n">
+        <v>89637</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>61021</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>40 &lt; 100 HP</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4465</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4762</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>32114</v>
+      </c>
+      <c r="H45" t="n">
+        <v>34243</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>26826</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>100+ HP</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>9597</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11404</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>6825</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Total 2WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14405</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15672</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>118680</v>
+      </c>
+      <c r="H47" t="n">
+        <v>135284</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>94672</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>166</v>
+      </c>
+      <c r="E48" t="n">
+        <v>171</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1209</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1599</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>507</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Total Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14571</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15843</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>119889</v>
+      </c>
+      <c r="H49" t="n">
+        <v>136883</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>95179</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>9/10/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Self-Prop Combines</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>387</v>
+      </c>
+      <c r="E50" t="n">
+        <v>403</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2063</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2269</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>987</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>August 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/7a3f3bc8-b2d4-43ab-b74f-5d46812506c1/August-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-11T11:22:10</t>
         </is>
       </c>
     </row>
@@ -2721,7 +3092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2829,561 +3200,652 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8829</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61021</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>40 &lt; 100 HP</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2738</v>
-      </c>
-      <c r="C11" t="n">
-        <v>23707</v>
-      </c>
+          <t>40 &lt; 100 HP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3789</v>
+        <v>2738</v>
       </c>
       <c r="C12" t="n">
-        <v>24777</v>
+        <v>23707</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4428</v>
+        <v>3789</v>
       </c>
       <c r="C13" t="n">
-        <v>24481</v>
+        <v>24777</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3986</v>
+        <v>4428</v>
       </c>
       <c r="C14" t="n">
-        <v>24867</v>
+        <v>24481</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4983</v>
+        <v>3986</v>
       </c>
       <c r="C15" t="n">
-        <v>25873</v>
+        <v>24867</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4983</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>July 2026</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>4794</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>26300</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100+ HP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4465</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26826</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>904</v>
-      </c>
-      <c r="C19" t="n">
-        <v>6301</v>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>March 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1164</v>
-      </c>
-      <c r="C20" t="n">
-        <v>6465</v>
-      </c>
+          <t>100+ HP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1733</v>
+        <v>904</v>
       </c>
       <c r="C21" t="n">
-        <v>6686</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1270</v>
+        <v>1164</v>
       </c>
       <c r="C22" t="n">
-        <v>6553</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1312</v>
+        <v>1733</v>
       </c>
       <c r="C23" t="n">
-        <v>6658</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1322</v>
+        <v>1270</v>
       </c>
       <c r="C24" t="n">
-        <v>6633</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6658</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Total 2WD Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1322</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6633</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9656</v>
+        <v>1111</v>
       </c>
       <c r="C27" t="n">
-        <v>90140</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>March 2026</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>14836</v>
-      </c>
-      <c r="C28" t="n">
-        <v>94470</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>19747</v>
-      </c>
-      <c r="C29" t="n">
-        <v>95117</v>
-      </c>
+          <t>Total 2WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16671</v>
+        <v>9656</v>
       </c>
       <c r="C30" t="n">
-        <v>93678</v>
+        <v>90140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18062</v>
+        <v>14836</v>
       </c>
       <c r="C31" t="n">
-        <v>94090</v>
+        <v>94470</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15833</v>
+        <v>19747</v>
       </c>
       <c r="C32" t="n">
-        <v>94755</v>
+        <v>95117</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>16671</v>
+      </c>
+      <c r="C33" t="n">
+        <v>93678</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4WD Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>18062</v>
+      </c>
+      <c r="C34" t="n">
+        <v>94090</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>148</v>
+        <v>15833</v>
       </c>
       <c r="C35" t="n">
-        <v>507</v>
+        <v>94755</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>225</v>
+        <v>14405</v>
       </c>
       <c r="C36" t="n">
-        <v>536</v>
+        <v>94672</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>167</v>
-      </c>
-      <c r="C37" t="n">
-        <v>519</v>
-      </c>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>144</v>
-      </c>
-      <c r="C38" t="n">
-        <v>513</v>
-      </c>
+          <t>4WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C39" t="n">
-        <v>457</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>152</v>
+        <v>225</v>
       </c>
       <c r="C40" t="n">
-        <v>465</v>
+        <v>536</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>167</v>
+      </c>
+      <c r="C41" t="n">
+        <v>519</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Total Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>144</v>
+      </c>
+      <c r="C42" t="n">
+        <v>513</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9804</v>
+        <v>124</v>
       </c>
       <c r="C43" t="n">
-        <v>90647</v>
+        <v>457</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15061</v>
+        <v>152</v>
       </c>
       <c r="C44" t="n">
-        <v>95006</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19914</v>
+        <v>166</v>
       </c>
       <c r="C45" t="n">
-        <v>95636</v>
+        <v>507</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>16815</v>
-      </c>
-      <c r="C46" t="n">
-        <v>94191</v>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>18186</v>
-      </c>
-      <c r="C47" t="n">
-        <v>94547</v>
-      </c>
+          <t>Total Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15985</v>
+        <v>9804</v>
       </c>
       <c r="C48" t="n">
-        <v>95220</v>
+        <v>90647</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>March 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>15061</v>
+      </c>
+      <c r="C49" t="n">
+        <v>95006</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Self-Prop Combines</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>19914</v>
+      </c>
+      <c r="C50" t="n">
+        <v>95636</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>159</v>
+        <v>16815</v>
       </c>
       <c r="C51" t="n">
-        <v>733</v>
+        <v>94191</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>180</v>
+        <v>18186</v>
       </c>
       <c r="C52" t="n">
-        <v>794</v>
+        <v>94547</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>428</v>
+        <v>15985</v>
       </c>
       <c r="C53" t="n">
-        <v>872</v>
+        <v>95220</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>138</v>
+        <v>14571</v>
       </c>
       <c r="C54" t="n">
-        <v>714</v>
+        <v>95179</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>269</v>
-      </c>
-      <c r="C55" t="n">
-        <v>841</v>
-      </c>
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Self-Prop Combines</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>159</v>
+      </c>
+      <c r="C57" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>March 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>180</v>
+      </c>
+      <c r="C58" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>428</v>
+      </c>
+      <c r="C59" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>138</v>
+      </c>
+      <c r="C60" t="n">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>269</v>
+      </c>
+      <c r="C61" t="n">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>July 2026</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B62" t="n">
         <v>340</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C62" t="n">
         <v>914</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>387</v>
+      </c>
+      <c r="C63" t="n">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-11T11:22:10</t>
+          <t>2026-09-12T10:47:50</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-12T10:47:50</t>
+          <t>2026-09-13T11:53:22</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-13T11:53:22</t>
+          <t>2026-09-14T12:48:36</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-14T12:48:36</t>
+          <t>2026-09-15T11:45:09</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-15T11:45:09</t>
+          <t>2026-09-16T11:35:18</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-16T11:35:18</t>
+          <t>2026-09-17T11:42:16</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-17T11:42:16</t>
+          <t>2026-09-18T11:15:43</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15:43</t>
+          <t>2026-09-20T11:25:16</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-20T11:25:16</t>
+          <t>2026-09-21T12:49:22</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-21T12:49:22</t>
+          <t>2026-09-22T11:39:29</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-22T11:39:29</t>
+          <t>2026-09-23T11:37:47</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-23T11:37:47</t>
+          <t>2026-09-24T11:46:57</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:57</t>
+          <t>2026-09-25T11:51:41</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-25T11:51:41</t>
+          <t>2026-09-26T11:25:50</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-26T11:25:50</t>
+          <t>2026-09-27T12:03:25</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-27T12:03:25</t>
+          <t>2026-09-28T13:56:15</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-28T13:56:15</t>
+          <t>2026-09-29T12:54:02</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-29T12:54:02</t>
+          <t>2026-09-30T12:35:28</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-30T12:35:28</t>
+          <t>2026-10-01T13:16:23</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-01T13:16:23</t>
+          <t>2026-10-02T12:35:57</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-02T12:35:57</t>
+          <t>2026-10-03T11:40:37</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-03T11:40:37</t>
+          <t>2026-10-04T12:22:39</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-04T12:22:39</t>
+          <t>2026-10-05T14:40:52</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-05T14:40:52</t>
+          <t>2026-10-06T13:18:58</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-06T13:18:58</t>
+          <t>2026-10-07T13:24:53</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-07T13:24:53</t>
+          <t>2026-10-08T13:30:22</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-08T13:30:22</t>
+          <t>2026-10-09T13:18:07</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-09T13:18:07</t>
+          <t>2026-10-10T12:32:56</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-10T12:32:56</t>
+          <t>2026-10-11T12:51:13</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-11T12:51:13</t>
+          <t>2026-10-12T15:26:47</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3078,377 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>2026-10-12T15:26:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>&lt; 40 HP</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>8952</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10578</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>86030</v>
+      </c>
+      <c r="H51" t="n">
+        <v>100212</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>61310</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>40 &lt; 100 HP</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4443</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5466</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>36853</v>
+      </c>
+      <c r="H52" t="n">
+        <v>39707</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>26485</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>100+ HP</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1396</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1643</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10994</v>
+      </c>
+      <c r="H53" t="n">
+        <v>13059</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7156</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Total 2WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14791</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17687</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="G54" t="n">
+        <v>133877</v>
+      </c>
+      <c r="H54" t="n">
+        <v>152978</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>94951</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>233</v>
+      </c>
+      <c r="E55" t="n">
+        <v>292</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1891</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>582</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Total Farm Tractors</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15024</v>
+      </c>
+      <c r="E56" t="n">
+        <v>17979</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>135325</v>
+      </c>
+      <c r="H56" t="n">
+        <v>154869</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>95533</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Self-Prop Combines</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>369</v>
+      </c>
+      <c r="E57" t="n">
+        <v>414</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2432</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2683</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>911</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>September 2026 Tractor and Combine Report U.S. Unit Retail Sales</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://www.aem.org/getattachment/dd9b4c30-f615-4bad-b1a0-809fe96aceed/September-2026-Farm_Flash_Trade_Press_With_Chart_PreRelease-United-States.pdf</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:12:41</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3213,639 +3584,730 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8952</v>
+      </c>
+      <c r="C10" t="n">
+        <v>61310</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>40 &lt; 100 HP</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2738</v>
-      </c>
-      <c r="C12" t="n">
-        <v>23707</v>
-      </c>
+          <t>40 &lt; 100 HP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3789</v>
+        <v>2738</v>
       </c>
       <c r="C13" t="n">
-        <v>24777</v>
+        <v>23707</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4428</v>
+        <v>3789</v>
       </c>
       <c r="C14" t="n">
-        <v>24481</v>
+        <v>24777</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3986</v>
+        <v>4428</v>
       </c>
       <c r="C15" t="n">
-        <v>24867</v>
+        <v>24481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4983</v>
+        <v>3986</v>
       </c>
       <c r="C16" t="n">
-        <v>25873</v>
+        <v>24867</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4794</v>
+        <v>4983</v>
       </c>
       <c r="C17" t="n">
-        <v>26300</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4794</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26300</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>August 2026</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>4465</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>26826</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100+ HP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4443</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26485</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>904</v>
-      </c>
-      <c r="C21" t="n">
-        <v>6301</v>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>March 2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1164</v>
-      </c>
-      <c r="C22" t="n">
-        <v>6465</v>
-      </c>
+          <t>100+ HP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1733</v>
+        <v>904</v>
       </c>
       <c r="C23" t="n">
-        <v>6686</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1270</v>
+        <v>1164</v>
       </c>
       <c r="C24" t="n">
-        <v>6553</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1312</v>
+        <v>1733</v>
       </c>
       <c r="C25" t="n">
-        <v>6658</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1322</v>
+        <v>1270</v>
       </c>
       <c r="C26" t="n">
-        <v>6633</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1111</v>
+        <v>1312</v>
       </c>
       <c r="C27" t="n">
-        <v>6825</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1322</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6633</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Total 2WD Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1111</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6825</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9656</v>
+        <v>1396</v>
       </c>
       <c r="C30" t="n">
-        <v>90140</v>
+        <v>7156</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>March 2026</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>14836</v>
-      </c>
-      <c r="C31" t="n">
-        <v>94470</v>
-      </c>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>19747</v>
-      </c>
-      <c r="C32" t="n">
-        <v>95117</v>
-      </c>
+          <t>Total 2WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16671</v>
+        <v>9656</v>
       </c>
       <c r="C33" t="n">
-        <v>93678</v>
+        <v>90140</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18062</v>
+        <v>14836</v>
       </c>
       <c r="C34" t="n">
-        <v>94090</v>
+        <v>94470</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15833</v>
+        <v>19747</v>
       </c>
       <c r="C35" t="n">
-        <v>94755</v>
+        <v>95117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14405</v>
+        <v>16671</v>
       </c>
       <c r="C36" t="n">
-        <v>94672</v>
+        <v>93678</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>18062</v>
+      </c>
+      <c r="C37" t="n">
+        <v>94090</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4WD Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>15833</v>
+      </c>
+      <c r="C38" t="n">
+        <v>94755</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>148</v>
+        <v>14405</v>
       </c>
       <c r="C39" t="n">
-        <v>507</v>
+        <v>94672</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>225</v>
+        <v>14791</v>
       </c>
       <c r="C40" t="n">
-        <v>536</v>
+        <v>94951</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>167</v>
-      </c>
-      <c r="C41" t="n">
-        <v>519</v>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>144</v>
-      </c>
-      <c r="C42" t="n">
-        <v>513</v>
-      </c>
+          <t>4WD Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C43" t="n">
-        <v>457</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>152</v>
+        <v>225</v>
       </c>
       <c r="C44" t="n">
-        <v>465</v>
+        <v>536</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C45" t="n">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>144</v>
+      </c>
+      <c r="C46" t="n">
+        <v>513</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Total Farm Tractors</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>124</v>
+      </c>
+      <c r="C47" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9804</v>
+        <v>152</v>
       </c>
       <c r="C48" t="n">
-        <v>90647</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15061</v>
+        <v>166</v>
       </c>
       <c r="C49" t="n">
-        <v>95006</v>
+        <v>507</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19914</v>
+        <v>233</v>
       </c>
       <c r="C50" t="n">
-        <v>95636</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>16815</v>
-      </c>
-      <c r="C51" t="n">
-        <v>94191</v>
-      </c>
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>18186</v>
-      </c>
-      <c r="C52" t="n">
-        <v>94547</v>
-      </c>
+          <t>Total Farm Tractors</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>July 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>15985</v>
+        <v>9804</v>
       </c>
       <c r="C53" t="n">
-        <v>95220</v>
+        <v>90647</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>March 2026</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>14571</v>
+        <v>15061</v>
       </c>
       <c r="C54" t="n">
-        <v>95179</v>
+        <v>95006</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>19914</v>
+      </c>
+      <c r="C55" t="n">
+        <v>95636</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Self-Prop Combines</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>16815</v>
+      </c>
+      <c r="C56" t="n">
+        <v>94191</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>159</v>
+        <v>18186</v>
       </c>
       <c r="C57" t="n">
-        <v>733</v>
+        <v>94547</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>180</v>
+        <v>15985</v>
       </c>
       <c r="C58" t="n">
-        <v>794</v>
+        <v>95220</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>428</v>
+        <v>14571</v>
       </c>
       <c r="C59" t="n">
-        <v>872</v>
+        <v>95179</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>138</v>
+        <v>15024</v>
       </c>
       <c r="C60" t="n">
-        <v>714</v>
+        <v>95533</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>269</v>
-      </c>
-      <c r="C61" t="n">
-        <v>841</v>
-      </c>
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>July 2026</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>340</v>
-      </c>
-      <c r="C62" t="n">
-        <v>914</v>
-      </c>
+          <t>Self-Prop Combines</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>159</v>
+      </c>
+      <c r="C63" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>March 2026</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>180</v>
+      </c>
+      <c r="C64" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>428</v>
+      </c>
+      <c r="C65" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>138</v>
+      </c>
+      <c r="C66" t="n">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>269</v>
+      </c>
+      <c r="C67" t="n">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>340</v>
+      </c>
+      <c r="C68" t="n">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>August 2026</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B69" t="n">
         <v>387</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C69" t="n">
         <v>987</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>369</v>
+      </c>
+      <c r="C70" t="n">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-13T14:12:41</t>
+          <t>2026-10-14T11:53:15</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-14T11:53:15</t>
+          <t>2026-10-15T11:30:11</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-15T11:30:11</t>
+          <t>2026-10-16T11:25:27</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-16T11:25:27</t>
+          <t>2026-10-17T10:44:58</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-17T10:44:58</t>
+          <t>2026-10-18T11:06:33</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:33</t>
+          <t>2026-10-19T13:16:53</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-19T13:16:53</t>
+          <t>2026-10-20T11:37:44</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:37:44</t>
+          <t>2026-10-21T11:50:09</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-21T11:50:09</t>
+          <t>2026-10-22T11:53:38</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-22T11:53:38</t>
+          <t>2026-10-23T11:40:00</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-23T11:40:00</t>
+          <t>2026-10-24T11:01:18</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-24T11:01:18</t>
+          <t>2026-10-25T11:30:44</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-25T11:30:44</t>
+          <t>2026-10-26T13:04:18</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-26T13:04:18</t>
+          <t>2026-10-27T12:12:37</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:37</t>
+          <t>2026-10-28T12:55:20</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-28T12:55:20</t>
+          <t>2026-10-29T13:01:42</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:42</t>
+          <t>2026-10-30T12:56:46</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-30T12:56:46</t>
+          <t>2026-10-31T12:30:31</t>
         </is>
       </c>
     </row>
